--- a/assets/templates/Student Database.xlsx
+++ b/assets/templates/Student Database.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Database" sheetId="1" r:id="R81bfb66ad80047c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="Rd2ba3c66f9194223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Database" sheetId="1" r:id="R661ed2624ea6454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="Rd52bf464dd094a59"/>
   </x:sheets>
 </x:workbook>
 </file>
